--- a/config/配置_奥林波斯.xlsx
+++ b/config/配置_奥林波斯.xlsx
@@ -355,7 +355,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,6 +370,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -858,133 +864,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1007,7 +1013,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1825,36 +1831,39 @@
       <c r="J2" s="2">
         <v>1</v>
       </c>
+      <c r="R2" s="5">
+        <v>50</v>
+      </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="5">
+      <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>89</v>
       </c>
       <c r="F3" s="2">
         <v>2000</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="6">
         <v>2000</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3" s="6">
         <v>502</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="6">
         <v>1</v>
       </c>
     </row>

--- a/config/配置_奥林波斯.xlsx
+++ b/config/配置_奥林波斯.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="3"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="107">
   <si>
     <t>key</t>
   </si>
@@ -132,7 +132,7 @@
     <t>north_modbus_conf</t>
   </si>
   <si>
-    <t>./config/MODBUS_REGISTERS.xlsx</t>
+    <t>./config/北向/MODBUS_REGISTERS.xlsx</t>
   </si>
   <si>
     <t>北向Modbus配置文件</t>
@@ -213,7 +213,7 @@
     <t>desc</t>
   </si>
   <si>
-    <t>pcs</t>
+    <t>pcs1</t>
   </si>
   <si>
     <t>PCS</t>
@@ -222,7 +222,10 @@
     <t>英博电气2.5MWPCS</t>
   </si>
   <si>
-    <t>bau</t>
+    <t>pcs2</t>
+  </si>
+  <si>
+    <t>bau1</t>
   </si>
   <si>
     <t>BAU</t>
@@ -231,6 +234,9 @@
     <t>高特电子</t>
   </si>
   <si>
+    <t>bau2</t>
+  </si>
+  <si>
     <t>meter</t>
   </si>
   <si>
@@ -258,6 +264,15 @@
     <t>爱可信_温湿度控制器</t>
   </si>
   <si>
+    <t>di</t>
+  </si>
+  <si>
+    <t>DI</t>
+  </si>
+  <si>
+    <t>IO模块</t>
+  </si>
+  <si>
     <t>comType</t>
   </si>
   <si>
@@ -300,40 +315,34 @@
     <t>ModbusTCP</t>
   </si>
   <si>
-    <t>./config/PCS_125_英博.xlsx</t>
+    <t>./config/pcs/PCS_英博_大机.xlsx</t>
   </si>
   <si>
     <t>192.168.0.20</t>
   </si>
   <si>
-    <t>./config/永泰_2_BCU.xlsx</t>
-  </si>
-  <si>
-    <t>can0</t>
-  </si>
-  <si>
-    <t>ModbusRTU</t>
-  </si>
-  <si>
-    <t>./config/除湿机.xlsx</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB1</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>./config/水冷机组_埃森特.xlsx</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB3</t>
-  </si>
-  <si>
-    <t>./config/消防温感烟感.xlsx</t>
-  </si>
-  <si>
-    <t>/dev/ttyXRUSB2</t>
+    <t>192.168.0.21</t>
+  </si>
+  <si>
+    <t>./config/bms/BAU_高特.xlsx</t>
+  </si>
+  <si>
+    <t>192.168.0.3</t>
+  </si>
+  <si>
+    <t>192.168.0.4</t>
+  </si>
+  <si>
+    <t>./config/组合测控/电表_乔宇电气.xlsx</t>
+  </si>
+  <si>
+    <t>192.168.0.5</t>
+  </si>
+  <si>
+    <t>./config/组合测控/干式变压器温湿度控制器.xlsx</t>
+  </si>
+  <si>
+    <t>./config/组合测控/温湿度控制器_爱可信.xlsx</t>
   </si>
   <si>
     <t>device_id</t>
@@ -994,7 +1003,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1011,6 +1020,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1383,7 +1395,7 @@
   <cols>
     <col min="1" max="1" width="17.5238095238095" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.0079365079365" style="1" customWidth="1"/>
-    <col min="3" max="3" width="31.1825396825397" style="1" customWidth="1"/>
+    <col min="3" max="3" width="35.0079365079365" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.1428571428571" style="1" customWidth="1"/>
     <col min="5" max="6" width="10.4206349206349" style="1" customWidth="1"/>
     <col min="7" max="7" width="20.6666666666667" style="1" customWidth="1"/>
@@ -1486,7 +1498,7 @@
         <v>28</v>
       </c>
       <c r="F6" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>29</v>
@@ -1620,8 +1632,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="6.46031746031746" style="2" customWidth="1"/>
     <col min="2" max="2" width="20.9285714285714" style="2" customWidth="1"/>
@@ -1663,14 +1675,14 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>65</v>
+      <c r="C3" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -1678,13 +1690,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1692,13 +1704,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1706,13 +1718,55 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D6" s="2" t="s">
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>74</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1752,16 +1806,16 @@
         <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>16</v>
@@ -1770,34 +1824,34 @@
         <v>20</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>59</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -1811,10 +1865,10 @@
         <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F2" s="2">
         <v>2000</v>
@@ -1823,7 +1877,7 @@
         <v>2000</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="I2" s="2">
         <v>502</v>
@@ -1840,16 +1894,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>61</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>89</v>
+        <v>93</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="F3" s="2">
         <v>2000</v>
@@ -1857,14 +1911,17 @@
       <c r="G3" s="6">
         <v>2000</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>90</v>
+      <c r="H3" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="I3" s="6">
         <v>502</v>
       </c>
       <c r="J3" s="6">
         <v>1</v>
+      </c>
+      <c r="R3" s="5">
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -1872,16 +1929,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F4" s="2">
         <v>2000</v>
@@ -1889,14 +1946,14 @@
       <c r="G4" s="2">
         <v>5000</v>
       </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="L4" s="2">
-        <v>500000</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>92</v>
+      <c r="H4" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I4" s="6">
+        <v>502</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -1904,16 +1961,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F5" s="2">
         <v>2000</v>
@@ -1921,14 +1978,14 @@
       <c r="G5" s="2">
         <v>5000</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="L5" s="2">
-        <v>500000</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>92</v>
+      <c r="H5" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I5" s="6">
+        <v>502</v>
+      </c>
+      <c r="J5" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1936,16 +1993,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2">
         <v>2000</v>
@@ -1953,22 +2010,13 @@
       <c r="G6" s="2">
         <v>2000</v>
       </c>
+      <c r="H6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8001</v>
+      </c>
       <c r="J6" s="2">
-        <v>2</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="L6" s="2">
-        <v>9600</v>
-      </c>
-      <c r="M6" s="2">
-        <v>8</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O6" s="2">
         <v>1</v>
       </c>
     </row>
@@ -1977,16 +2025,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F7" s="2">
         <v>2000</v>
@@ -1994,22 +2042,13 @@
       <c r="G7" s="2">
         <v>2000</v>
       </c>
-      <c r="J7" s="2">
-        <v>1</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L7" s="2">
-        <v>9600</v>
-      </c>
-      <c r="M7" s="2">
-        <v>8</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="H7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8002</v>
+      </c>
+      <c r="J7" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2018,16 +2057,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>93</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F8" s="2">
         <v>2000</v>
@@ -2035,22 +2074,13 @@
       <c r="G8" s="2">
         <v>2000</v>
       </c>
-      <c r="J8" s="2">
-        <v>1</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="L8" s="2">
-        <v>9600</v>
-      </c>
-      <c r="M8" s="2">
-        <v>8</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="O8" s="2">
+      <c r="H8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8003</v>
+      </c>
+      <c r="J8" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2078,13 +2108,13 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>13</v>

--- a/config/配置_奥林波斯.xlsx
+++ b/config/配置_奥林波斯.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="2"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="109">
   <si>
     <t>key</t>
   </si>
@@ -318,10 +318,10 @@
     <t>./config/pcs/PCS_英博_大机.xlsx</t>
   </si>
   <si>
-    <t>192.168.0.20</t>
-  </si>
-  <si>
-    <t>192.168.0.21</t>
+    <t>192.168.0.32</t>
+  </si>
+  <si>
+    <t>192.168.0.33</t>
   </si>
   <si>
     <t>./config/bms/BAU_高特.xlsx</t>
@@ -343,6 +343,12 @@
   </si>
   <si>
     <t>./config/组合测控/温湿度控制器_爱可信.xlsx</t>
+  </si>
+  <si>
+    <t>./config/组合测控/DI.xlsx</t>
+  </si>
+  <si>
+    <t>192.168.0.6</t>
   </si>
   <si>
     <t>device_id</t>
@@ -1003,7 +1009,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1020,9 +1026,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1675,13 +1678,13 @@
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1779,8 +1782,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:S8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelRow="7"/>
+  <dimension ref="A1:S9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="6.46031746031746" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.5952380952381" style="2" customWidth="1"/>
@@ -2081,6 +2084,38 @@
         <v>8003</v>
       </c>
       <c r="J8" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" s="2">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F9" s="2">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I9" s="2">
+        <v>502</v>
+      </c>
+      <c r="J9" s="2">
         <v>1</v>
       </c>
     </row>
@@ -2108,13 +2143,13 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>13</v>

--- a/config/配置_奥林波斯.xlsx
+++ b/config/配置_奥林波斯.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="3"/>
+    <workbookView windowWidth="15404" windowHeight="11268"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -1893,8 +1893,8 @@
       </c>
     </row>
     <row r="3" spans="1:19">
-      <c r="A3" s="6">
-        <v>1</v>
+      <c r="A3" s="2">
+        <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>63</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>64</v>
@@ -1961,7 +1961,7 @@
     </row>
     <row r="5" spans="1:19">
       <c r="A5" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>67</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>68</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="7" spans="1:19">
       <c r="A7" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>71</v>
@@ -2057,7 +2057,7 @@
     </row>
     <row r="8" spans="1:19">
       <c r="A8" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>74</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="9" spans="1:19">
       <c r="A9" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>77</v>

--- a/config/配置_奥林波斯.xlsx
+++ b/config/配置_奥林波斯.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="15404" windowHeight="11268"/>
+    <workbookView windowWidth="22010" windowHeight="12332" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="112">
   <si>
     <t>key</t>
   </si>
@@ -225,16 +225,22 @@
     <t>pcs2</t>
   </si>
   <si>
-    <t>bau1</t>
+    <t>bau</t>
   </si>
   <si>
     <t>BAU</t>
   </si>
   <si>
-    <t>高特电子</t>
-  </si>
-  <si>
-    <t>bau2</t>
+    <t>高特电子BMS</t>
+  </si>
+  <si>
+    <t>ems</t>
+  </si>
+  <si>
+    <t>EMS</t>
+  </si>
+  <si>
+    <t>高特电子EMS</t>
   </si>
   <si>
     <t>meter</t>
@@ -327,10 +333,13 @@
     <t>./config/bms/BAU_高特.xlsx</t>
   </si>
   <si>
+    <t>192.168.0.4</t>
+  </si>
+  <si>
+    <t>./config/ems/EMS_高特.xlsx</t>
+  </si>
+  <si>
     <t>192.168.0.3</t>
-  </si>
-  <si>
-    <t>192.168.0.4</t>
   </si>
   <si>
     <t>./config/组合测控/电表_乔宇电气.xlsx</t>
@@ -1710,10 +1719,10 @@
         <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -1721,13 +1730,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -1735,13 +1744,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -1749,13 +1758,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -1763,13 +1772,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1809,16 +1818,16 @@
         <v>58</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>16</v>
@@ -1827,34 +1836,34 @@
         <v>20</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q1" s="1" t="s">
         <v>59</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:19">
@@ -1868,10 +1877,10 @@
         <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F2" s="2">
         <v>2000</v>
@@ -1880,7 +1889,7 @@
         <v>2000</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I2" s="2">
         <v>502</v>
@@ -1903,10 +1912,10 @@
         <v>61</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F3" s="2">
         <v>2000</v>
@@ -1915,7 +1924,7 @@
         <v>2000</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I3" s="6">
         <v>502</v>
@@ -1938,10 +1947,10 @@
         <v>65</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F4" s="2">
         <v>2000</v>
@@ -1950,7 +1959,7 @@
         <v>5000</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I4" s="6">
         <v>502</v>
@@ -1967,13 +1976,13 @@
         <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F5" s="2">
         <v>2000</v>
@@ -1982,7 +1991,7 @@
         <v>5000</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="I5" s="6">
         <v>502</v>
@@ -1996,16 +2005,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F6" s="2">
         <v>2000</v>
@@ -2014,7 +2023,7 @@
         <v>2000</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I6" s="2">
         <v>8001</v>
@@ -2028,16 +2037,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F7" s="2">
         <v>2000</v>
@@ -2046,7 +2055,7 @@
         <v>2000</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I7" s="2">
         <v>8002</v>
@@ -2060,16 +2069,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F8" s="2">
         <v>2000</v>
@@ -2078,7 +2087,7 @@
         <v>2000</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="I8" s="2">
         <v>8003</v>
@@ -2092,16 +2101,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F9" s="2">
         <v>2000</v>
@@ -2110,7 +2119,7 @@
         <v>2000</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2">
         <v>502</v>
@@ -2143,13 +2152,13 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>13</v>

--- a/config/配置_奥林波斯.xlsx
+++ b/config/配置_奥林波斯.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="22010" windowHeight="12332" activeTab="3"/>
+    <workbookView windowWidth="24771" windowHeight="10748" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
@@ -1352,11 +1352,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultColWidth="22.4047619047619" defaultRowHeight="18" outlineLevelRow="2" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="22.4031007751938" defaultRowHeight="18.4" outlineLevelRow="2" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="22.4047619047619" style="2"/>
-    <col min="2" max="2" width="33.7936507936508" style="2" customWidth="1"/>
-    <col min="3" max="16384" width="22.4047619047619" style="2"/>
+    <col min="1" max="1" width="22.4031007751938" style="2"/>
+    <col min="2" max="2" width="33.7906976744186" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="22.4031007751938" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1403,15 +1403,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultColWidth="9.03174603174603" defaultRowHeight="18" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.03100775193798" defaultRowHeight="18.4" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="17.5238095238095" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.0079365079365" style="1" customWidth="1"/>
-    <col min="3" max="3" width="35.0079365079365" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.1428571428571" style="1" customWidth="1"/>
-    <col min="5" max="6" width="10.4206349206349" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5271317829457" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.0077519379845" style="1" customWidth="1"/>
+    <col min="3" max="3" width="35.0077519379845" style="1" customWidth="1"/>
+    <col min="4" max="4" width="19.1395348837209" style="1" customWidth="1"/>
+    <col min="5" max="6" width="10.4186046511628" style="1" customWidth="1"/>
     <col min="7" max="7" width="20.6666666666667" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.03174603174603" style="1"/>
+    <col min="8" max="16384" width="9.03100775193798" style="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
@@ -1645,12 +1645,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="6.46031746031746" style="2" customWidth="1"/>
-    <col min="2" max="2" width="20.9285714285714" style="2" customWidth="1"/>
-    <col min="3" max="3" width="21.8571428571429" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23.1111111111111" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.45736434108527" style="2" customWidth="1"/>
+    <col min="2" max="2" width="20.9302325581395" style="2" customWidth="1"/>
+    <col min="3" max="3" width="21.8604651162791" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23.1085271317829" style="2" customWidth="1"/>
     <col min="5" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -1792,19 +1792,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:S9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.4"/>
   <cols>
-    <col min="1" max="1" width="6.46031746031746" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.5952380952381" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.4603174603175" style="2" customWidth="1"/>
-    <col min="4" max="4" width="12.9285714285714" style="2" customWidth="1"/>
-    <col min="5" max="5" width="44.531746031746" style="2" customWidth="1"/>
-    <col min="6" max="10" width="12.1984126984127" style="2" customWidth="1"/>
+    <col min="1" max="1" width="6.45736434108527" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.5968992248062" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.4573643410853" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.9302325581395" style="2" customWidth="1"/>
+    <col min="5" max="5" width="44.5348837209302" style="2" customWidth="1"/>
+    <col min="6" max="10" width="12.2015503875969" style="2" customWidth="1"/>
     <col min="11" max="11" width="16.6666666666667" style="2" customWidth="1"/>
-    <col min="12" max="16" width="12.1984126984127" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9.07142857142857" style="2"/>
-    <col min="18" max="18" width="15.2142857142857" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9.07142857142857" style="2"/>
+    <col min="12" max="16" width="12.2015503875969" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.06976744186047" style="2"/>
+    <col min="18" max="18" width="15.2170542635659" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9.06976744186047" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:19">
@@ -1898,7 +1898,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="5">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:19">
@@ -1933,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="R3" s="5">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:19">
@@ -2139,15 +2139,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultColWidth="9.11111111111111" defaultRowHeight="18" outlineLevelRow="5" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9.10852713178295" defaultRowHeight="18.4" outlineLevelRow="5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="11.7619047619048" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.6746031746032" style="3" customWidth="1"/>
-    <col min="3" max="3" width="144.857142857143" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.3968253968254" style="3" customWidth="1"/>
-    <col min="5" max="5" width="10.2936507936508" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.4365079365079" style="3" customWidth="1"/>
-    <col min="7" max="16384" width="9.11111111111111" style="3"/>
+    <col min="1" max="1" width="11.7596899224806" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20.6744186046512" style="3" customWidth="1"/>
+    <col min="3" max="3" width="144.860465116279" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.3953488372093" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.2945736434109" style="3" customWidth="1"/>
+    <col min="6" max="6" width="10.4341085271318" style="3" customWidth="1"/>
+    <col min="7" max="16384" width="9.10852713178295" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:7">
